--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_90/per_file_predictions_epoch_90.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run1/epoch_90/per_file_predictions_epoch_90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="499">
   <si>
     <t>Filename</t>
   </si>
@@ -808,691 +808,709 @@
     <t>0,1,1,0</t>
   </si>
   <si>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
     <t>0,1,0,1</t>
   </si>
   <si>
-    <t>0.9820,0.0028,0.0024,0.0023</t>
-  </si>
-  <si>
-    <t>0.0004,0.0310,0.0000,0.9976</t>
-  </si>
-  <si>
-    <t>0.9993,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0072,0.0006,0.0000,0.9978</t>
+    <t>1,1,0,0</t>
+  </si>
+  <si>
+    <t>0.9846,0.0018,0.0028,0.0005</t>
+  </si>
+  <si>
+    <t>0.0007,0.0514,0.0000,0.9967</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.0492,0.0007,0.0000,0.9785</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0009,0.0002,0.0004</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0010,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9973,0.0000,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.0010,0.0002,0.9986,0.0003</t>
+  </si>
+  <si>
+    <t>0.7502,0.0001,0.3521,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0051,0.9911,0.0004,0.0008</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9919,0.0001,0.0045,0.0001</t>
+  </si>
+  <si>
+    <t>0.6549,0.0002,0.3603,0.0009</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0076,0.0005,0.9881,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.3679,0.5566,0.0047,0.0002</t>
+  </si>
+  <si>
+    <t>0.8537,0.1400,0.0036,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0004</t>
+  </si>
+  <si>
+    <t>0.0044,0.9832,0.0248,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0019,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.3046,0.0071,0.6470,0.0010</t>
+  </si>
+  <si>
+    <t>0.3076,0.7211,0.0006,0.0006</t>
+  </si>
+  <si>
+    <t>0.0044,0.9840,0.0342,0.0001</t>
+  </si>
+  <si>
+    <t>0.0105,0.9262,0.0151,0.0025</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0017,0.0035,0.9957,0.0002</t>
+  </si>
+  <si>
+    <t>0.0010,0.0000,0.9965,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0044,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9996,0.0005</t>
+  </si>
+  <si>
+    <t>0.0087,0.4980,0.0273,0.8365</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.0164,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0006,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0176,0.0109,0.9762,0.0007</t>
+  </si>
+  <si>
+    <t>0.0064,0.0008,0.9928,0.0007</t>
+  </si>
+  <si>
+    <t>0.0001,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0015,0.9981,0.0002</t>
+  </si>
+  <si>
+    <t>0.9997,0.0002,0.0001,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9996,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9978,0.0017,0.0003,0.0002</t>
+    <t>0.9922,0.0013,0.0050,0.0003</t>
+  </si>
+  <si>
+    <t>0.0003,0.0017,0.9997,0.0006</t>
+  </si>
+  <si>
+    <t>0.9970,0.0009,0.0006,0.0003</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9725,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0004,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0026,0.0028,0.9915,0.0055</t>
+  </si>
+  <si>
+    <t>0.0000,0.9910,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0184,0.9832,0.0015,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9321,0.0011,0.0411,0.0008</t>
+  </si>
+  <si>
+    <t>0.8732,0.0048,0.0581,0.0011</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.9793,0.9852,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.6974,0.8955,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.0280,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9981,0.9200,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0023,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0011,0.0001,1.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.0001,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9988,0.3750,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.8574,0.9887,0.0000</t>
+  </si>
+  <si>
+    <t>0.0035,0.9725,0.0311,0.0017</t>
+  </si>
+  <si>
+    <t>0.0000,0.4816,0.9985,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9710,0.9952,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9944,0.9625,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0006,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0005,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.9980,0.0007,0.0005,0.0005</t>
+  </si>
+  <si>
+    <t>0.9980,0.0016,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9999,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9994,0.0006,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0020,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0006,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9949,0.0001,0.0027,0.0000</t>
-  </si>
-  <si>
-    <t>0.0030,0.0007,0.9960,0.0001</t>
-  </si>
-  <si>
-    <t>0.8612,0.0003,0.2144,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0001,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0047,0.9928,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9727,0.0006,0.0136,0.0006</t>
-  </si>
-  <si>
-    <t>0.7151,0.0001,0.4446,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9993,0.0001</t>
-  </si>
-  <si>
-    <t>0.0007,0.0003,0.9989,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0001,0.9962,0.0006</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.9431,0.0198,0.0076,0.0004</t>
-  </si>
-  <si>
-    <t>0.9592,0.0186,0.0045,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0022</t>
-  </si>
-  <si>
-    <t>0.0040,0.9879,0.0108,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9955,0.0013,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.7367,0.2556,0.0005,0.0010</t>
-  </si>
-  <si>
-    <t>0.0002,0.9902,0.5579,0.0000</t>
-  </si>
-  <si>
-    <t>0.0303,0.0878,0.3969,0.0286</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0241,0.9991,0.0001</t>
-  </si>
-  <si>
-    <t>0.0085,0.0000,0.9562,0.0020</t>
-  </si>
-  <si>
-    <t>0.0000,0.0071,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9748,0.0008,0.7721</t>
-  </si>
-  <si>
-    <t>0.0001,0.9991,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9983,0.0575,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0003,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.0402,0.9927,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0010,0.9979,0.0032</t>
-  </si>
-  <si>
-    <t>0.0019,0.0001,0.9988,0.0000</t>
-  </si>
-  <si>
-    <t>0.0005,0.0005,0.9992,0.0001</t>
-  </si>
-  <si>
-    <t>0.0296,0.0004,0.9679,0.0009</t>
-  </si>
-  <si>
-    <t>0.9988,0.0006,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0012,0.0007,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.0029,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9981,0.0005,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9963,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.9940,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0025,0.9994,0.0003</t>
-  </si>
-  <si>
-    <t>0.0029,0.0028,0.9927,0.0010</t>
-  </si>
-  <si>
-    <t>0.0000,0.9956,0.9847,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0033,0.9920,0.0089,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9978,0.0001,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0270,0.0016,0.9730,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0006,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9959,0.9705,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8967,0.9881,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9995,0.0056,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9971,0.9902,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.0010,0.9991</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0003,0.9999</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0003,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.9975,0.8465,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.8480,0.9880,0.0001</t>
-  </si>
-  <si>
-    <t>0.0015,0.9560,0.1338,0.0014</t>
-  </si>
-  <si>
-    <t>0.0001,0.2883,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9937,0.9928,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.0602,0.9911,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9989,0.0011,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0005,0.0000,0.0001</t>
-  </si>
-  <si>
     <t>0.9997,0.0001,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9973,0.0013,0.0004,0.0007</t>
-  </si>
-  <si>
-    <t>0.9965,0.0039,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
+    <t>0.9992,0.0002,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.0053,0.0016,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0019,0.9962,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.0007,0.9985,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.1686,0.8413,0.0024,0.0003</t>
+  </si>
+  <si>
+    <t>0.0688,0.0028,0.8312,0.0143</t>
+  </si>
+  <si>
+    <t>0.4935,0.0010,0.4803,0.0004</t>
+  </si>
+  <si>
+    <t>0.9787,0.0034,0.0021,0.0003</t>
+  </si>
+  <si>
+    <t>0.7009,0.0010,0.3154,0.0009</t>
+  </si>
+  <si>
+    <t>0.0001,0.8867,0.0066,0.5944</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9783,0.9969,0.0000</t>
+  </si>
+  <si>
+    <t>0.0041,0.9953,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9273,0.0615,0.0032,0.0005</t>
+  </si>
+  <si>
+    <t>0.9288,0.0746,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0004,0.0004,0.0005</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.1974,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.4250,0.9962,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0106,0.9977,0.0001</t>
+  </si>
+  <si>
+    <t>0.1004,0.0006,0.9370,0.0001</t>
+  </si>
+  <si>
+    <t>0.9985,0.0000,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.0741,0.0025,0.9192,0.0011</t>
+  </si>
+  <si>
+    <t>0.0123,0.0000,0.9920,0.0001</t>
+  </si>
+  <si>
+    <t>0.1803,0.0061,0.8157,0.0006</t>
+  </si>
+  <si>
+    <t>0.0075,0.0010,0.0004,0.9975</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0003,1.0000</t>
+  </si>
+  <si>
+    <t>0.0023,0.0000,0.0000,0.9995</t>
+  </si>
+  <si>
+    <t>0.0000,0.9970,0.9893,0.0000</t>
+  </si>
+  <si>
+    <t>0.9986,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0044,0.9911,0.0004,0.0302</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9769,0.0207,0.0009,0.0005</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0039,0.0002,0.0002,0.9978</t>
+  </si>
+  <si>
+    <t>0.0012,0.0120,0.9961,0.0082</t>
+  </si>
+  <si>
+    <t>0.8160,0.0001,0.0070,0.0855</t>
+  </si>
+  <si>
+    <t>0.9990,0.0001,0.0001,0.0010</t>
+  </si>
+  <si>
+    <t>0.1181,0.8937,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9987,0.0001,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.8889,0.1070,0.0027,0.0006</t>
+  </si>
+  <si>
+    <t>0.9533,0.0143,0.0118,0.0005</t>
+  </si>
+  <si>
+    <t>0.9955,0.0004,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0002,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0006,0.0005,0.0006</t>
+  </si>
+  <si>
+    <t>0.9982,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.9988,0.0003,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0010,0.0014</t>
+  </si>
+  <si>
+    <t>0.8779,0.0721,0.0001,0.0009</t>
+  </si>
+  <si>
+    <t>0.9860,0.0101,0.0003,0.0004</t>
+  </si>
+  <si>
+    <t>0.5242,0.5328,0.0013,0.0009</t>
+  </si>
+  <si>
+    <t>0.0208,0.0174,0.9741,0.0010</t>
+  </si>
+  <si>
+    <t>0.5692,0.5151,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9554,0.0119,0.0099,0.0020</t>
+  </si>
+  <si>
+    <t>0.9993,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9937,0.0035,0.0001,0.0007</t>
+  </si>
+  <si>
+    <t>0.0000,0.0015,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9903,0.0059,0.0018,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0457,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0020,0.0004,0.9986,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0017,0.9993,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0017,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0222,0.0008,0.9773,0.0006</t>
+  </si>
+  <si>
+    <t>0.0185,0.0028,0.9717,0.0006</t>
+  </si>
+  <si>
+    <t>0.4801,0.0007,0.5462,0.0005</t>
+  </si>
+  <si>
+    <t>0.0453,0.0540,0.7459,0.0002</t>
+  </si>
+  <si>
+    <t>0.0037,0.0046,0.9907,0.0003</t>
+  </si>
+  <si>
+    <t>0.1010,0.0030,0.9108,0.0002</t>
+  </si>
+  <si>
+    <t>0.0381,0.0009,0.9645,0.0006</t>
+  </si>
+  <si>
+    <t>0.0057,0.0009,0.9926,0.0003</t>
+  </si>
+  <si>
+    <t>0.0646,0.9622,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.9992,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.1168,0.9054,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.9500,0.0458,0.0009,0.0006</t>
+  </si>
+  <si>
+    <t>0.0190,0.9826,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.6749,0.1086,0.0081,0.0011</t>
+  </si>
+  <si>
+    <t>0.9969,0.0001,0.0015,0.0000</t>
+  </si>
+  <si>
+    <t>0.9908,0.0005,0.0014,0.0002</t>
+  </si>
+  <si>
+    <t>0.7736,0.0285,0.1485,0.0020</t>
+  </si>
+  <si>
+    <t>0.9072,0.0010,0.0702,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9994,0.0002</t>
+  </si>
+  <si>
+    <t>0.0047,0.0021,0.9844,0.0030</t>
+  </si>
+  <si>
+    <t>0.0002,0.0010,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.1155,0.0002,0.8989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0042,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9993,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0023,0.0011,0.0012</t>
+  </si>
+  <si>
+    <t>0.9449,0.0801,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0004,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9978,0.0011,0.0003,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0003,0.0002,0.0005</t>
   </si>
   <si>
     <t>0.9996,0.0001,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9993,0.0002,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9988,0.0001</t>
-  </si>
-  <si>
-    <t>0.9879,0.0006,0.0036,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0004,0.9987,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.0017,0.9965,0.0011,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0671,0.9224,0.0043,0.0006</t>
-  </si>
-  <si>
-    <t>0.0730,0.0009,0.7902,0.0312</t>
-  </si>
-  <si>
-    <t>0.9183,0.0006,0.0850,0.0001</t>
-  </si>
-  <si>
-    <t>0.9457,0.0032,0.0168,0.0027</t>
-  </si>
-  <si>
-    <t>0.9022,0.0036,0.0519,0.0020</t>
-  </si>
-  <si>
-    <t>0.0002,0.0717,0.0011,0.9824</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0002,0.0009</t>
-  </si>
-  <si>
-    <t>0.0000,0.9900,0.9992,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.9986,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0672,0.9271,0.0072,0.0005</t>
-  </si>
-  <si>
-    <t>0.1696,0.8512,0.0025,0.0001</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0004,0.0006,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0001,0.0012,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0765,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.1390,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.0841,0.9957,0.0000</t>
-  </si>
-  <si>
-    <t>0.0093,0.0053,0.9873,0.0000</t>
-  </si>
-  <si>
-    <t>0.9966,0.0001,0.0010,0.0001</t>
-  </si>
-  <si>
-    <t>0.9518,0.0008,0.0376,0.0002</t>
-  </si>
-  <si>
-    <t>0.0258,0.0000,0.9858,0.0001</t>
-  </si>
-  <si>
-    <t>0.0629,0.0064,0.9337,0.0002</t>
-  </si>
-  <si>
-    <t>0.0069,0.0001,0.0008,0.9966</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,1.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9936,0.6545,0.0000</t>
-  </si>
-  <si>
-    <t>0.9954,0.0024,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.0027,0.9942,0.0005,0.0114</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.8404,0.1753,0.0029,0.0009</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0039,0.0001,0.0002,0.9980</t>
-  </si>
-  <si>
-    <t>0.0007,0.0055,0.9980,0.0055</t>
-  </si>
-  <si>
-    <t>0.2574,0.0000,0.1656,0.0331</t>
-  </si>
-  <si>
-    <t>0.9928,0.0005,0.0012,0.0034</t>
-  </si>
-  <si>
-    <t>0.7906,0.1569,0.0081,0.0007</t>
-  </si>
-  <si>
-    <t>0.9966,0.0007,0.0009,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.2925,0.4923,0.0154,0.0039</t>
-  </si>
-  <si>
-    <t>0.9939,0.0006,0.0018,0.0004</t>
-  </si>
-  <si>
-    <t>0.9981,0.0001,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0005,0.0007</t>
-  </si>
-  <si>
-    <t>0.9076,0.0475,0.0002,0.0014</t>
-  </si>
-  <si>
-    <t>0.8403,0.1606,0.0003,0.0005</t>
-  </si>
-  <si>
-    <t>0.8811,0.1437,0.0003,0.0003</t>
-  </si>
-  <si>
-    <t>0.9890,0.0082,0.0009,0.0013</t>
-  </si>
-  <si>
-    <t>0.9249,0.1047,0.0004,0.0003</t>
-  </si>
-  <si>
-    <t>0.9903,0.0018,0.0022,0.0006</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9916,0.0064,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9673,0.0173,0.0071,0.0009</t>
-  </si>
-  <si>
-    <t>0.0010,0.0104,0.9963,0.0009</t>
-  </si>
-  <si>
-    <t>0.0003,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0010,0.0097,0.9951,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0009,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0006,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0019,0.0013,0.9965,0.0003</t>
-  </si>
-  <si>
-    <t>0.0625,0.0011,0.9385,0.0009</t>
-  </si>
-  <si>
-    <t>0.3200,0.0047,0.6884,0.0003</t>
-  </si>
-  <si>
-    <t>0.0833,0.0023,0.9107,0.0003</t>
-  </si>
-  <si>
-    <t>0.0051,0.0219,0.9775,0.0003</t>
-  </si>
-  <si>
-    <t>0.8086,0.0017,0.2216,0.0001</t>
-  </si>
-  <si>
-    <t>0.8399,0.0006,0.1449,0.0007</t>
-  </si>
-  <si>
-    <t>0.0276,0.0010,0.9765,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.9984,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0151,0.9889,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9451,0.0766,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.6311,0.3854,0.0017,0.0013</t>
-  </si>
-  <si>
-    <t>0.0593,0.9448,0.0004,0.0008</t>
-  </si>
-  <si>
-    <t>0.7782,0.0567,0.0058,0.0057</t>
-  </si>
-  <si>
-    <t>0.9979,0.0000,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.8363,0.0135,0.0135,0.0206</t>
-  </si>
-  <si>
-    <t>0.9833,0.0005,0.0120,0.0001</t>
-  </si>
-  <si>
-    <t>0.8533,0.0006,0.0920,0.0061</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9998,0.0001</t>
-  </si>
-  <si>
-    <t>0.0357,0.0069,0.8662,0.0096</t>
-  </si>
-  <si>
-    <t>0.0001,0.0004,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0002,0.9954,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0049,0.9975,0.0003</t>
-  </si>
-  <si>
-    <t>0.9984,0.0006,0.0002,0.0007</t>
-  </si>
-  <si>
-    <t>0.9976,0.0007,0.0005,0.0008</t>
-  </si>
-  <si>
-    <t>0.9791,0.0174,0.0016,0.0013</t>
-  </si>
-  <si>
-    <t>0.9982,0.0010,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9979,0.0012,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.9965,0.0018,0.0004,0.0006</t>
-  </si>
-  <si>
-    <t>0.9985,0.0005,0.0003,0.0006</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0007,0.9998,0.0003</t>
-  </si>
-  <si>
-    <t>0.0376,0.0265,0.9264,0.0017</t>
-  </si>
-  <si>
-    <t>0.9578,0.0005,0.0257,0.0008</t>
-  </si>
-  <si>
-    <t>0.0005,0.0002,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0001,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.3584,0.9932,0.0001</t>
-  </si>
-  <si>
-    <t>0.0038,0.0005,0.9959,0.0002</t>
-  </si>
-  <si>
-    <t>0.0017,0.0039,0.9952,0.0025</t>
-  </si>
-  <si>
-    <t>0.0007,0.0005,0.9982,0.0003</t>
-  </si>
-  <si>
-    <t>0.9917,0.0002,0.0024,0.0002</t>
-  </si>
-  <si>
-    <t>0.9891,0.0000,0.0075,0.0001</t>
-  </si>
-  <si>
-    <t>0.9873,0.0001,0.0082,0.0002</t>
-  </si>
-  <si>
-    <t>0.9974,0.0013,0.0003,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0023,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9975,0.0018,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9972,0.0009,0.0009,0.0006</t>
-  </si>
-  <si>
-    <t>0.0049,0.0022,0.9915,0.0014</t>
-  </si>
-  <si>
-    <t>0.0000,0.0015,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9992,0.0004</t>
-  </si>
-  <si>
-    <t>0.0005,0.0028,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0015,0.0006,0.9978,0.0001</t>
-  </si>
-  <si>
-    <t>0.0016,0.0007,0.9938,0.0143</t>
-  </si>
-  <si>
-    <t>0.0023,0.0011,0.9968,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9987,0.0004</t>
-  </si>
-  <si>
-    <t>0.9609,0.0007,0.0005,0.0443</t>
-  </si>
-  <si>
-    <t>0.0001,0.0290,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0013,0.0001,0.0020,0.9989</t>
-  </si>
-  <si>
-    <t>0.9107,0.0008,0.0266,0.0143</t>
+    <t>0.0005,0.0076,0.9987,0.0007</t>
+  </si>
+  <si>
+    <t>0.0355,0.0319,0.9323,0.0004</t>
+  </si>
+  <si>
+    <t>0.9237,0.0002,0.0360,0.0028</t>
+  </si>
+  <si>
+    <t>0.0010,0.0001,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.2772,0.8357,0.0016</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0043,0.0004,0.9951,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0006,0.9981,0.0007</t>
+  </si>
+  <si>
+    <t>0.0020,0.0018,0.9955,0.0005</t>
+  </si>
+  <si>
+    <t>0.9831,0.0005,0.0071,0.0003</t>
+  </si>
+  <si>
+    <t>0.8472,0.0001,0.1834,0.0002</t>
+  </si>
+  <si>
+    <t>0.9935,0.0002,0.0024,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0005,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0004,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9993,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0031,0.0004,0.0002</t>
+  </si>
+  <si>
+    <t>0.9989,0.0008,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0348,0.0053,0.9656,0.0019</t>
+  </si>
+  <si>
+    <t>0.0002,0.0024,0.9989,0.0004</t>
+  </si>
+  <si>
+    <t>0.0001,0.0046,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0011,0.0006,0.9978,0.0009</t>
+  </si>
+  <si>
+    <t>0.0017,0.0012,0.9847,0.0186</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9979,0.0010</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.9854,0.0005,0.0002,0.0120</t>
+  </si>
+  <si>
+    <t>0.0001,0.0052,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0017,0.0001,0.0004,0.9991</t>
+  </si>
+  <si>
+    <t>0.9705,0.0005,0.0076,0.0044</t>
   </si>
 </sst>
 </file>
@@ -1878,7 +1896,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1892,7 +1910,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1906,7 +1924,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1920,7 +1938,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1934,7 +1952,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1948,7 +1966,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1962,7 +1980,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1976,7 +1994,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1990,7 +2008,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -2004,7 +2022,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2018,7 +2036,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -2032,7 +2050,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2046,7 +2064,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2060,7 +2078,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2074,7 +2092,7 @@
         <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2088,7 +2106,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2102,7 +2120,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2116,7 +2134,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2130,7 +2148,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2144,7 +2162,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2158,7 +2176,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2172,7 +2190,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2186,7 +2204,7 @@
         <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2200,7 +2218,7 @@
         <v>259</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2214,7 +2232,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2228,7 +2246,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2242,7 +2260,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2256,7 +2274,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2270,7 +2288,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2281,10 +2299,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2298,7 +2316,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2312,7 +2330,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2326,7 +2344,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2340,7 +2358,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2351,10 +2369,10 @@
         <v>259</v>
       </c>
       <c r="C36" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D36" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2365,10 +2383,10 @@
         <v>259</v>
       </c>
       <c r="C37" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2379,10 +2397,10 @@
         <v>262</v>
       </c>
       <c r="C38" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2393,10 +2411,10 @@
         <v>263</v>
       </c>
       <c r="C39" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2410,7 +2428,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2424,7 +2442,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2438,7 +2456,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2452,7 +2470,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2466,7 +2484,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2480,7 +2498,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2491,10 +2509,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2508,7 +2526,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2522,7 +2540,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2536,7 +2554,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2550,7 +2568,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2564,7 +2582,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2578,7 +2596,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2592,7 +2610,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2606,7 +2624,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2620,7 +2638,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2634,7 +2652,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2648,7 +2666,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2662,7 +2680,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2676,7 +2694,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2690,7 +2708,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2704,7 +2722,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2718,7 +2736,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2732,7 +2750,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2746,7 +2764,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2760,7 +2778,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2774,7 +2792,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2788,7 +2806,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>294</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2802,7 +2820,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2816,7 +2834,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2830,7 +2848,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2841,10 +2859,10 @@
         <v>261</v>
       </c>
       <c r="C71" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D71" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2858,7 +2876,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2872,7 +2890,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2886,7 +2904,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2900,7 +2918,7 @@
         <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2914,7 +2932,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2928,7 +2946,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2942,7 +2960,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2956,7 +2974,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2970,7 +2988,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2984,7 +3002,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2998,7 +3016,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3009,10 +3027,10 @@
         <v>263</v>
       </c>
       <c r="C83" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D83" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3026,7 +3044,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3040,7 +3058,7 @@
         <v>262</v>
       </c>
       <c r="D85" t="s">
-        <v>343</v>
+        <v>345</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3054,7 +3072,7 @@
         <v>261</v>
       </c>
       <c r="D86" t="s">
-        <v>344</v>
+        <v>346</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3068,7 +3086,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>345</v>
+        <v>347</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3079,10 +3097,10 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>346</v>
+        <v>348</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3096,7 +3114,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>347</v>
+        <v>275</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3110,7 +3128,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3124,7 +3142,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3138,7 +3156,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>272</v>
+        <v>351</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3152,7 +3170,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>352</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3166,7 +3184,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>353</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3180,7 +3198,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>354</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3194,7 +3212,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>355</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3208,7 +3226,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3222,7 +3240,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3236,7 +3254,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>354</v>
+        <v>277</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3250,7 +3268,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3264,7 +3282,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>356</v>
+        <v>358</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3278,7 +3296,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>355</v>
+        <v>357</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3292,7 +3310,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3306,7 +3324,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3320,7 +3338,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>358</v>
+        <v>360</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3334,7 +3352,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>359</v>
+        <v>361</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3348,7 +3366,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>360</v>
+        <v>362</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3362,7 +3380,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3376,7 +3394,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3390,7 +3408,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3404,7 +3422,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3418,7 +3436,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3432,7 +3450,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>365</v>
+        <v>284</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3446,7 +3464,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>282</v>
+        <v>367</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3460,7 +3478,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3474,7 +3492,7 @@
         <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3485,10 +3503,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D117" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3502,7 +3520,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3516,7 +3534,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3527,10 +3545,10 @@
         <v>262</v>
       </c>
       <c r="C120" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="D120" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3544,7 +3562,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3558,7 +3576,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3572,7 +3590,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3586,7 +3604,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3600,7 +3618,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3611,10 +3629,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3625,10 +3643,10 @@
         <v>259</v>
       </c>
       <c r="C127" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3642,7 +3660,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3656,7 +3674,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3670,7 +3688,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>356</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3684,7 +3702,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3698,7 +3716,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3712,7 +3730,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3726,7 +3744,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>272</v>
+        <v>387</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3740,7 +3758,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3754,7 +3772,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3768,7 +3786,7 @@
         <v>261</v>
       </c>
       <c r="D137" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3782,7 +3800,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3796,7 +3814,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3810,7 +3828,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3821,10 +3839,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3838,7 +3856,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3852,7 +3870,7 @@
         <v>261</v>
       </c>
       <c r="D143" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3866,7 +3884,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3880,7 +3898,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3894,7 +3912,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3908,7 +3926,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3922,7 +3940,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3936,7 +3954,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3950,7 +3968,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3964,7 +3982,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3978,7 +3996,7 @@
         <v>259</v>
       </c>
       <c r="D152" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3992,7 +4010,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -4006,7 +4024,7 @@
         <v>260</v>
       </c>
       <c r="D154" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4020,7 +4038,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>399</v>
+        <v>320</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4034,7 +4052,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4048,7 +4066,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4062,7 +4080,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4073,10 +4091,10 @@
         <v>259</v>
       </c>
       <c r="C159" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4090,7 +4108,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4104,7 +4122,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4118,7 +4136,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4132,7 +4150,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4146,7 +4164,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4160,7 +4178,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4174,7 +4192,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4188,7 +4206,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4202,7 +4220,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>272</v>
+        <v>357</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4216,7 +4234,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>379</v>
+        <v>418</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4230,7 +4248,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4244,7 +4262,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4258,7 +4276,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4272,7 +4290,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>417</v>
+        <v>422</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4286,7 +4304,7 @@
         <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>418</v>
+        <v>423</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4297,10 +4315,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D175" t="s">
-        <v>419</v>
+        <v>424</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4311,10 +4329,10 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
-        <v>420</v>
+        <v>425</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4325,10 +4343,10 @@
         <v>259</v>
       </c>
       <c r="C177" t="s">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="D177" t="s">
-        <v>421</v>
+        <v>426</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4342,7 +4360,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>422</v>
+        <v>427</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4356,7 +4374,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>423</v>
+        <v>428</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4370,7 +4388,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>424</v>
+        <v>429</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4384,7 +4402,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>425</v>
+        <v>430</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4398,7 +4416,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>426</v>
+        <v>431</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4412,7 +4430,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4426,7 +4444,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>427</v>
+        <v>432</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4440,7 +4458,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>428</v>
+        <v>433</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4454,7 +4472,7 @@
         <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>429</v>
+        <v>434</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4468,7 +4486,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>430</v>
+        <v>435</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4482,7 +4500,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>431</v>
+        <v>363</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4496,7 +4514,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4510,7 +4528,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4524,7 +4542,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4538,7 +4556,7 @@
         <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4552,7 +4570,7 @@
         <v>261</v>
       </c>
       <c r="D193" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4566,7 +4584,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4577,10 +4595,10 @@
         <v>261</v>
       </c>
       <c r="C195" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D195" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4591,10 +4609,10 @@
         <v>259</v>
       </c>
       <c r="C196" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D196" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4608,7 +4626,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4622,7 +4640,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4636,7 +4654,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4647,10 +4665,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4664,7 +4682,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4678,7 +4696,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4692,7 +4710,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4706,7 +4724,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4720,7 +4738,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4734,7 +4752,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4748,7 +4766,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4762,7 +4780,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4776,7 +4794,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4790,7 +4808,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4804,7 +4822,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4818,7 +4836,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4832,7 +4850,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4846,7 +4864,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4860,7 +4878,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4874,7 +4892,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4888,7 +4906,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4902,7 +4920,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4916,7 +4934,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4930,7 +4948,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4944,7 +4962,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4958,7 +4976,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4972,7 +4990,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4986,7 +5004,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -5000,7 +5018,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -5014,7 +5032,7 @@
         <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5028,7 +5046,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>287</v>
+        <v>474</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5042,7 +5060,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>470</v>
+        <v>475</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5056,7 +5074,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>287</v>
+        <v>294</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5070,7 +5088,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>471</v>
+        <v>476</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5084,7 +5102,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>472</v>
+        <v>477</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5098,7 +5116,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>473</v>
+        <v>478</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5112,7 +5130,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>474</v>
+        <v>479</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5126,7 +5144,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>475</v>
+        <v>480</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5140,7 +5158,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>476</v>
+        <v>481</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5154,7 +5172,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>477</v>
+        <v>482</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5168,7 +5186,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>355</v>
+        <v>483</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5182,7 +5200,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5196,7 +5214,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>479</v>
+        <v>357</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5210,7 +5228,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>382</v>
+        <v>485</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5224,7 +5242,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>272</v>
+        <v>486</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5238,7 +5256,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>480</v>
+        <v>487</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5252,7 +5270,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>481</v>
+        <v>488</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5266,7 +5284,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>482</v>
+        <v>291</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5280,7 +5298,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>483</v>
+        <v>489</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5294,7 +5312,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>484</v>
+        <v>490</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5308,7 +5326,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>485</v>
+        <v>491</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5322,7 +5340,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>486</v>
+        <v>492</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5336,7 +5354,7 @@
         <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>487</v>
+        <v>493</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5350,7 +5368,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>488</v>
+        <v>494</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5364,7 +5382,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>489</v>
+        <v>495</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5378,7 +5396,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>490</v>
+        <v>496</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5392,7 +5410,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>491</v>
+        <v>497</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5406,7 +5424,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5420,7 +5438,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5434,7 +5452,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>492</v>
+        <v>498</v>
       </c>
     </row>
   </sheetData>
